--- a/Result/profitability/2230.xlsx
+++ b/Result/profitability/2230.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM69"/>
+  <dimension ref="A1:AM70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.35</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06749999999999996</v>
+        <v>-0.13625</v>
       </c>
       <c r="N2" t="n">
-        <v>10.02375</v>
+        <v>7.30125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.76</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.008750000000000049</v>
+        <v>-0.1725000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>9.5975</v>
+        <v>8.86125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -801,7 +801,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.1</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1275000000000001</v>
+        <v>-0.18125</v>
       </c>
       <c r="N4" t="n">
-        <v>10.66125</v>
+        <v>10.135</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.2</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.12375</v>
+        <v>-0.11625</v>
       </c>
       <c r="N5" t="n">
-        <v>12.69375</v>
+        <v>11.85625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.57</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.01250000000000004</v>
+        <v>-0.04250000000000005</v>
       </c>
       <c r="N6" t="n">
-        <v>14.51</v>
+        <v>13.745</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.001250000000000038</v>
+        <v>0.07249999999999995</v>
       </c>
       <c r="N7" t="n">
-        <v>15.91875</v>
+        <v>15.96</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,13 +1391,13 @@
         <v>0.13</v>
       </c>
       <c r="M8" t="n">
-        <v>0.12125</v>
+        <v>0.2399999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>17.86</v>
+        <v>18.46375</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.26</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3049999999999999</v>
+        <v>0.305</v>
       </c>
       <c r="N9" t="n">
         <v>20.3575</v>
@@ -9195,6 +9195,133 @@
       </c>
       <c r="AM69" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2230</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>427</v>
+      </c>
+      <c r="D70" t="n">
+        <v>413</v>
+      </c>
+      <c r="E70" t="n">
+        <v>13</v>
+      </c>
+      <c r="F70" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-25</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-5.95%</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>-26</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="M70" t="n">
+        <v>-0.008750000000000036</v>
+      </c>
+      <c r="N70" t="n">
+        <v>8.0825</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="X70" t="n">
+        <v>-0.7851239669421488</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>-2.857988165680474</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>-0.1875</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>-6.699999999999999</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>-0.6808943089430894</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK70" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
